--- a/tests/testthat/fixtures/ex3/tables/irt_poly_booklet1.xlsx
+++ b/tests/testthat/fixtures/ex3/tables/irt_poly_booklet1.xlsx
@@ -148,22 +148,22 @@
     <t xml:space="preserve">step3</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29 (0.12)</t>
+    <t xml:space="preserve">0.29 (0.10)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.29</t>
   </si>
   <si>
-    <t xml:space="preserve">0.93 (0.132)</t>
+    <t xml:space="preserve">0.93 (0.13)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.93</t>
   </si>
   <si>
-    <t xml:space="preserve">0.95 (0.092)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.01 (0.092)</t>
+    <t xml:space="preserve">0.95 (0.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.01 (0.09)</t>
   </si>
   <si>
     <t xml:space="preserve">0.06</t>
